--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/108.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/108.xlsx
@@ -426,13 +426,13 @@
         <v>-16.06545982491859</v>
       </c>
       <c r="E2">
-        <v>-4.868514669139919</v>
+        <v>-11.63047734213337</v>
       </c>
       <c r="F2">
-        <v>-4.975343434120377</v>
+        <v>-4.964897309902138</v>
       </c>
       <c r="G2">
-        <v>-17.03625057576252</v>
+        <v>-16.6156739046352</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.04927439344227</v>
       </c>
       <c r="E3">
-        <v>-5.833143031409812</v>
+        <v>-11.47633714386029</v>
       </c>
       <c r="F3">
-        <v>-5.273240100520453</v>
+        <v>-4.890957248122102</v>
       </c>
       <c r="G3">
-        <v>-16.80140378575216</v>
+        <v>-17.38017322020079</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.95371508569477</v>
       </c>
       <c r="E4">
-        <v>-6.073903880501614</v>
+        <v>-11.92270429832235</v>
       </c>
       <c r="F4">
-        <v>-4.717327650082898</v>
+        <v>-4.767337915480645</v>
       </c>
       <c r="G4">
-        <v>-16.31069651792092</v>
+        <v>-16.48493880601661</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.90917623798898</v>
       </c>
       <c r="E5">
-        <v>-5.248295141793194</v>
+        <v>-11.83236124186933</v>
       </c>
       <c r="F5">
-        <v>-4.341869778327133</v>
+        <v>-4.412495935479113</v>
       </c>
       <c r="G5">
-        <v>-16.15046280327466</v>
+        <v>-17.44531813532257</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.88684389882639</v>
       </c>
       <c r="E6">
-        <v>-7.732584283083098</v>
+        <v>-15.04645019728737</v>
       </c>
       <c r="F6">
-        <v>-4.340313787265214</v>
+        <v>-4.488794927220197</v>
       </c>
       <c r="G6">
-        <v>-16.59568152012354</v>
+        <v>-18.28741829360144</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.90771637159128</v>
       </c>
       <c r="E7">
-        <v>-8.768060621202993</v>
+        <v>-14.21626317135719</v>
       </c>
       <c r="F7">
-        <v>-4.496309611788957</v>
+        <v>-4.702707668924519</v>
       </c>
       <c r="G7">
-        <v>-17.42212941909274</v>
+        <v>-17.38820460367906</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.948496104997197</v>
       </c>
       <c r="E8">
-        <v>-8.586292203009114</v>
+        <v>-15.63373440592012</v>
       </c>
       <c r="F8">
-        <v>-3.88357220939952</v>
+        <v>-3.838115890361619</v>
       </c>
       <c r="G8">
-        <v>-16.48650138351115</v>
+        <v>-16.64990494551127</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.021738685713974</v>
       </c>
       <c r="E9">
-        <v>-10.20875387047725</v>
+        <v>-15.79316839030817</v>
       </c>
       <c r="F9">
-        <v>-3.779030198215446</v>
+        <v>-4.004397884806141</v>
       </c>
       <c r="G9">
-        <v>-16.40549067889241</v>
+        <v>-16.12084997342588</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.119386638730559</v>
       </c>
       <c r="E10">
-        <v>-11.14983869638126</v>
+        <v>-16.71262069587754</v>
       </c>
       <c r="F10">
-        <v>-3.902994778746469</v>
+        <v>-4.04878203493929</v>
       </c>
       <c r="G10">
-        <v>-16.838798052891</v>
+        <v>-16.46909287979289</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.246658417515233</v>
       </c>
       <c r="E11">
-        <v>-11.61616736426913</v>
+        <v>-16.74088743063342</v>
       </c>
       <c r="F11">
-        <v>-3.492299450372176</v>
+        <v>-4.180399082453715</v>
       </c>
       <c r="G11">
-        <v>-16.6515221470072</v>
+        <v>-16.60663942585853</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.418957498454578</v>
       </c>
       <c r="E12">
-        <v>-12.02893324159428</v>
+        <v>-17.30813314178222</v>
       </c>
       <c r="F12">
-        <v>-3.53691798898081</v>
+        <v>-3.662872495994582</v>
       </c>
       <c r="G12">
-        <v>-16.21581793803818</v>
+        <v>-16.37058263145357</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.641706203446319</v>
       </c>
       <c r="E13">
-        <v>-12.30310064344067</v>
+        <v>-18.63556019917663</v>
       </c>
       <c r="F13">
-        <v>-3.37503473771642</v>
+        <v>-3.765293133104924</v>
       </c>
       <c r="G13">
-        <v>-15.78646004486794</v>
+        <v>-17.47128439925984</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.940421435657606</v>
       </c>
       <c r="E14">
-        <v>-13.68186248218602</v>
+        <v>-18.76692217319113</v>
       </c>
       <c r="F14">
-        <v>-3.059956445839742</v>
+        <v>-4.025738322016688</v>
       </c>
       <c r="G14">
-        <v>-15.39578918686963</v>
+        <v>-15.70648719627577</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.335279088034044</v>
       </c>
       <c r="E15">
-        <v>-14.13735451177354</v>
+        <v>-20.53613809782584</v>
       </c>
       <c r="F15">
-        <v>-3.008365641938387</v>
+        <v>-3.422621933063545</v>
       </c>
       <c r="G15">
-        <v>-15.29243395513358</v>
+        <v>-14.88024620640277</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.841724037565861</v>
       </c>
       <c r="E16">
-        <v>-14.67646481391269</v>
+        <v>-21.34528583351637</v>
       </c>
       <c r="F16">
-        <v>-2.484031495601737</v>
+        <v>-3.090065070851119</v>
       </c>
       <c r="G16">
-        <v>-15.10914891189737</v>
+        <v>-14.61765704477332</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.485862228623736</v>
       </c>
       <c r="E17">
-        <v>-16.18192429844464</v>
+        <v>-22.06537659937207</v>
       </c>
       <c r="F17">
-        <v>-2.654291759305843</v>
+        <v>-2.80904675024484</v>
       </c>
       <c r="G17">
-        <v>-14.04126623729466</v>
+        <v>-13.325506428431</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.275057403711203</v>
       </c>
       <c r="E18">
-        <v>-16.14295225113463</v>
+        <v>-22.44652467117566</v>
       </c>
       <c r="F18">
-        <v>-2.202953786023628</v>
+        <v>-2.908042623313044</v>
       </c>
       <c r="G18">
-        <v>-13.05476339313832</v>
+        <v>-13.28598513578318</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.214301317595338</v>
       </c>
       <c r="E19">
-        <v>-17.76914085271108</v>
+        <v>-22.67835536952434</v>
       </c>
       <c r="F19">
-        <v>-1.919067374004488</v>
+        <v>-2.286444386326723</v>
       </c>
       <c r="G19">
-        <v>-12.79439560756572</v>
+        <v>-15.42942432954862</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.304274895666452</v>
       </c>
       <c r="E20">
-        <v>-18.51880708231087</v>
+        <v>-24.68940086311666</v>
       </c>
       <c r="F20">
-        <v>-1.08480831484</v>
+        <v>-2.130641773924663</v>
       </c>
       <c r="G20">
-        <v>-11.70790766703231</v>
+        <v>-13.56510881710852</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.527572299184782</v>
       </c>
       <c r="E21">
-        <v>-19.3419976158992</v>
+        <v>-24.05261590510607</v>
       </c>
       <c r="F21">
-        <v>-1.271331654589754</v>
+        <v>-2.326964294026199</v>
       </c>
       <c r="G21">
-        <v>-12.58833732156487</v>
+        <v>-13.54817041085684</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.871410678725419</v>
       </c>
       <c r="E22">
-        <v>-19.83177925067279</v>
+        <v>-24.04660662009789</v>
       </c>
       <c r="F22">
-        <v>-0.954713208710311</v>
+        <v>-1.439573485104633</v>
       </c>
       <c r="G22">
-        <v>-11.59570003652425</v>
+        <v>-12.85939485868377</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.309253179846945</v>
       </c>
       <c r="E23">
-        <v>-20.64676418935922</v>
+        <v>-26.66050974443533</v>
       </c>
       <c r="F23">
-        <v>-0.8550886043936771</v>
+        <v>-1.318636158430972</v>
       </c>
       <c r="G23">
-        <v>-11.79730232822925</v>
+        <v>-13.2008445256042</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.805927624745772</v>
       </c>
       <c r="E24">
-        <v>-19.52322261721216</v>
+        <v>-26.33306484588871</v>
       </c>
       <c r="F24">
-        <v>-0.7055305444161951</v>
+        <v>-1.478517605418247</v>
       </c>
       <c r="G24">
-        <v>-11.64364997811506</v>
+        <v>-12.51580657934497</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.331861973898323</v>
       </c>
       <c r="E25">
-        <v>-21.17289588499238</v>
+        <v>-26.31631854900834</v>
       </c>
       <c r="F25">
-        <v>-0.6507454056833983</v>
+        <v>-0.9792978674886352</v>
       </c>
       <c r="G25">
-        <v>-11.97848186450248</v>
+        <v>-12.804661609283</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.847926923148816</v>
       </c>
       <c r="E26">
-        <v>-21.6407868764129</v>
+        <v>-25.35984596842626</v>
       </c>
       <c r="F26">
-        <v>-0.4453617121866759</v>
+        <v>-0.9220777809108502</v>
       </c>
       <c r="G26">
-        <v>-12.55224575409573</v>
+        <v>-13.44488139003158</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.32404679231359</v>
       </c>
       <c r="E27">
-        <v>-19.7737513847385</v>
+        <v>-26.59664920397917</v>
       </c>
       <c r="F27">
-        <v>-0.580137461149446</v>
+        <v>-0.8573683490589521</v>
       </c>
       <c r="G27">
-        <v>-12.33308432885044</v>
+        <v>-12.3745820171852</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.73264123672492</v>
       </c>
       <c r="E28">
-        <v>-22.44010782350679</v>
+        <v>-25.81476741028881</v>
       </c>
       <c r="F28">
-        <v>-0.3693406608337515</v>
+        <v>-0.9482184307510938</v>
       </c>
       <c r="G28">
-        <v>-11.97408877057187</v>
+        <v>-13.40069884926447</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.047041697180115</v>
       </c>
       <c r="E29">
-        <v>-21.08314605863436</v>
+        <v>-28.90075489297788</v>
       </c>
       <c r="F29">
-        <v>-0.1419331610239704</v>
+        <v>-0.7431633562318249</v>
       </c>
       <c r="G29">
-        <v>-11.64494440142091</v>
+        <v>-13.71919981450667</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.253538638516023</v>
       </c>
       <c r="E30">
-        <v>-20.98216561673732</v>
+        <v>-27.09788787799217</v>
       </c>
       <c r="F30">
-        <v>-0.2043359252100309</v>
+        <v>-0.9571148987310749</v>
       </c>
       <c r="G30">
-        <v>-13.07056131645172</v>
+        <v>-12.63129827102799</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.339814868200478</v>
       </c>
       <c r="E31">
-        <v>-20.9980922598223</v>
+        <v>-26.73092751525461</v>
       </c>
       <c r="F31">
-        <v>-0.1949936440148536</v>
+        <v>-0.8811722408209648</v>
       </c>
       <c r="G31">
-        <v>-12.57763101729086</v>
+        <v>-14.55119784307245</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.303121552412594</v>
       </c>
       <c r="E32">
-        <v>-20.97815791724053</v>
+        <v>-25.57186459299138</v>
       </c>
       <c r="F32">
-        <v>-0.406813518351922</v>
+        <v>-0.09458035415233089</v>
       </c>
       <c r="G32">
-        <v>-12.34609808336531</v>
+        <v>-12.28264154646856</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.151691273896253</v>
       </c>
       <c r="E33">
-        <v>-20.79757595923666</v>
+        <v>-25.35115129833154</v>
       </c>
       <c r="F33">
-        <v>-0.4688037271470106</v>
+        <v>-1.041161379810489</v>
       </c>
       <c r="G33">
-        <v>-11.68509138717565</v>
+        <v>-12.90385217473064</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.896819147270467</v>
       </c>
       <c r="E34">
-        <v>-20.44133902294926</v>
+        <v>-26.01122619816358</v>
       </c>
       <c r="F34">
-        <v>-0.3682597815464641</v>
+        <v>-1.269558695817419</v>
       </c>
       <c r="G34">
-        <v>-11.96135641242783</v>
+        <v>-14.66918072027377</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.562073027706766</v>
       </c>
       <c r="E35">
-        <v>-19.91747609279394</v>
+        <v>-24.52530707897472</v>
       </c>
       <c r="F35">
-        <v>-0.7289147541106162</v>
+        <v>-1.348964918564596</v>
       </c>
       <c r="G35">
-        <v>-10.92116976180667</v>
+        <v>-12.65176075300622</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.170440778883867</v>
       </c>
       <c r="E36">
-        <v>-18.88906870260002</v>
+        <v>-27.28914797770613</v>
       </c>
       <c r="F36">
-        <v>-0.2732477207085476</v>
+        <v>-1.226129520351281</v>
       </c>
       <c r="G36">
-        <v>-11.22226056805785</v>
+        <v>-13.27380232819866</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.746575943202858</v>
       </c>
       <c r="E37">
-        <v>-18.67277067009765</v>
+        <v>-25.59079361434344</v>
       </c>
       <c r="F37">
-        <v>-0.5130477193066424</v>
+        <v>-1.543272172888735</v>
       </c>
       <c r="G37">
-        <v>-11.08567739074413</v>
+        <v>-12.78811881322326</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.318207474145049</v>
       </c>
       <c r="E38">
-        <v>-19.30764914055101</v>
+        <v>-25.49667381056802</v>
       </c>
       <c r="F38">
-        <v>-0.8698202368190948</v>
+        <v>-1.327344957259974</v>
       </c>
       <c r="G38">
-        <v>-10.81637775330658</v>
+        <v>-12.10667611941968</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.900886166201408</v>
       </c>
       <c r="E39">
-        <v>-17.71267983878344</v>
+        <v>-23.77036517715599</v>
       </c>
       <c r="F39">
-        <v>-0.5888660563023905</v>
+        <v>-0.8934000341940728</v>
       </c>
       <c r="G39">
-        <v>-11.18444420636275</v>
+        <v>-12.10234592585432</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.513100926836489</v>
       </c>
       <c r="E40">
-        <v>-18.0511244006947</v>
+        <v>-23.60777484638459</v>
       </c>
       <c r="F40">
-        <v>-0.7992803916395064</v>
+        <v>-1.36839619829408</v>
       </c>
       <c r="G40">
-        <v>-10.05815026626514</v>
+        <v>-12.41315649380879</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.164026422798568</v>
       </c>
       <c r="E41">
-        <v>-16.58492678580925</v>
+        <v>-22.8772323625192</v>
       </c>
       <c r="F41">
-        <v>-0.6443211026374182</v>
+        <v>-0.9767314720526655</v>
       </c>
       <c r="G41">
-        <v>-9.962597990365159</v>
+        <v>-12.8969695505545</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.85637865852848</v>
       </c>
       <c r="E42">
-        <v>-16.49560716448196</v>
+        <v>-23.52151647348649</v>
       </c>
       <c r="F42">
-        <v>-1.283316349104842</v>
+        <v>-0.9577079965964069</v>
       </c>
       <c r="G42">
-        <v>-10.29887658515325</v>
+        <v>-12.15212659912834</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.597551865571173</v>
       </c>
       <c r="E43">
-        <v>-16.54158476108184</v>
+        <v>-22.98464776598114</v>
       </c>
       <c r="F43">
-        <v>-1.342622176373261</v>
+        <v>-1.359685023906205</v>
       </c>
       <c r="G43">
-        <v>-9.180978188543232</v>
+        <v>-11.44965200951377</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.385312614460418</v>
       </c>
       <c r="E44">
-        <v>-16.00526852740542</v>
+        <v>-22.24522041611269</v>
       </c>
       <c r="F44">
-        <v>-1.465410855262069</v>
+        <v>-1.819955890404456</v>
       </c>
       <c r="G44">
-        <v>-9.749799433646347</v>
+        <v>-11.48214170343617</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.222182614799464</v>
       </c>
       <c r="E45">
-        <v>-16.50205571146888</v>
+        <v>-20.8037980825232</v>
       </c>
       <c r="F45">
-        <v>-1.506922954717568</v>
+        <v>-1.462794573089764</v>
       </c>
       <c r="G45">
-        <v>-9.703710018648612</v>
+        <v>-11.00000709327887</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.106888411566231</v>
       </c>
       <c r="E46">
-        <v>-15.23122099374834</v>
+        <v>-22.90516851867251</v>
       </c>
       <c r="F46">
-        <v>-1.934082489788769</v>
+        <v>-1.124581505200346</v>
       </c>
       <c r="G46">
-        <v>-9.562879411408018</v>
+        <v>-11.17380411299953</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.029489665790475</v>
       </c>
       <c r="E47">
-        <v>-14.4098554351851</v>
+        <v>-21.96834498680972</v>
       </c>
       <c r="F47">
-        <v>-1.409132281851013</v>
+        <v>-1.588317520241579</v>
       </c>
       <c r="G47">
-        <v>-9.429967629097357</v>
+        <v>-11.02582603793965</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.985586669089708</v>
       </c>
       <c r="E48">
-        <v>-13.76882276855532</v>
+        <v>-21.29229363067862</v>
       </c>
       <c r="F48">
-        <v>-1.819723877487845</v>
+        <v>-1.661415050474602</v>
       </c>
       <c r="G48">
-        <v>-9.37222509380139</v>
+        <v>-12.17055640614546</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.966881650947595</v>
       </c>
       <c r="E49">
-        <v>-14.73597801932149</v>
+        <v>-20.08316389978659</v>
       </c>
       <c r="F49">
-        <v>-1.885341564682247</v>
+        <v>-2.175753636925956</v>
       </c>
       <c r="G49">
-        <v>-9.239164336941462</v>
+        <v>-11.5548776994795</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.969961322505866</v>
       </c>
       <c r="E50">
-        <v>-13.83620646178945</v>
+        <v>-20.38691582232508</v>
       </c>
       <c r="F50">
-        <v>-2.003420302178539</v>
+        <v>-2.498246839898721</v>
       </c>
       <c r="G50">
-        <v>-9.434059463383896</v>
+        <v>-11.74961060919051</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.000646686822169</v>
       </c>
       <c r="E51">
-        <v>-11.06850730320351</v>
+        <v>-19.17652717565892</v>
       </c>
       <c r="F51">
-        <v>-2.147216840035652</v>
+        <v>-1.891245620335005</v>
       </c>
       <c r="G51">
-        <v>-8.577697474921843</v>
+        <v>-11.1740623355516</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.059173061952474</v>
       </c>
       <c r="E52">
-        <v>-11.60391331360438</v>
+        <v>-18.13073950222356</v>
       </c>
       <c r="F52">
-        <v>-2.40767786600657</v>
+        <v>-2.09877444349419</v>
       </c>
       <c r="G52">
-        <v>-8.189396967529648</v>
+        <v>-11.7129728017074</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.150743751315024</v>
       </c>
       <c r="E53">
-        <v>-12.07615164007226</v>
+        <v>-18.14269467360381</v>
       </c>
       <c r="F53">
-        <v>-2.475409800598085</v>
+        <v>-2.144115943853222</v>
       </c>
       <c r="G53">
-        <v>-9.382742696979653</v>
+        <v>-10.34245329608667</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.276504855181748</v>
       </c>
       <c r="E54">
-        <v>-11.76585607259268</v>
+        <v>-17.97322106234075</v>
       </c>
       <c r="F54">
-        <v>-2.610314621592963</v>
+        <v>-1.086799033175707</v>
       </c>
       <c r="G54">
-        <v>-10.11553857318841</v>
+        <v>-11.04308060129033</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.431820910356626</v>
       </c>
       <c r="E55">
-        <v>-11.43326229909933</v>
+        <v>-18.68316804641927</v>
       </c>
       <c r="F55">
-        <v>-2.531802400835052</v>
+        <v>-2.766365083970789</v>
       </c>
       <c r="G55">
-        <v>-9.14950483210138</v>
+        <v>-9.64812926958979</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.619665487013677</v>
       </c>
       <c r="E56">
-        <v>-10.44196575339826</v>
+        <v>-17.48920870345293</v>
       </c>
       <c r="F56">
-        <v>-2.591277684636423</v>
+        <v>-2.335188478845076</v>
       </c>
       <c r="G56">
-        <v>-8.673276235186142</v>
+        <v>-10.95533128122641</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.836994910591131</v>
       </c>
       <c r="E57">
-        <v>-10.74968461916748</v>
+        <v>-15.52464346707534</v>
       </c>
       <c r="F57">
-        <v>-2.700790156836103</v>
+        <v>-3.131081470355086</v>
       </c>
       <c r="G57">
-        <v>-8.718223511972827</v>
+        <v>-11.29290760986589</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.08449211146233</v>
       </c>
       <c r="E58">
-        <v>-9.780324001559572</v>
+        <v>-16.49991374326326</v>
       </c>
       <c r="F58">
-        <v>-2.881361929755636</v>
+        <v>-2.862356666917405</v>
       </c>
       <c r="G58">
-        <v>-8.726453528183455</v>
+        <v>-11.673276050146</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.363876614831359</v>
       </c>
       <c r="E59">
-        <v>-8.433071284959587</v>
+        <v>-15.19253876877482</v>
       </c>
       <c r="F59">
-        <v>-2.408186235605426</v>
+        <v>-3.208257043320365</v>
       </c>
       <c r="G59">
-        <v>-8.389757804657417</v>
+        <v>-11.88408496899571</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.668623440654256</v>
       </c>
       <c r="E60">
-        <v>-8.676617145566107</v>
+        <v>-15.72649566749323</v>
       </c>
       <c r="F60">
-        <v>-2.995976310561904</v>
+        <v>-3.027207783067328</v>
       </c>
       <c r="G60">
-        <v>-8.885492135890043</v>
+        <v>-11.98615570906252</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.999243910563079</v>
       </c>
       <c r="E61">
-        <v>-9.390992977224121</v>
+        <v>-15.43970288011346</v>
       </c>
       <c r="F61">
-        <v>-2.801524147146502</v>
+        <v>-3.11700549217866</v>
       </c>
       <c r="G61">
-        <v>-9.129893160326738</v>
+        <v>-11.61864873820248</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.349055631295767</v>
       </c>
       <c r="E62">
-        <v>-7.477037966356252</v>
+        <v>-13.81417543574213</v>
       </c>
       <c r="F62">
-        <v>-2.831700871512243</v>
+        <v>-3.131631808160701</v>
       </c>
       <c r="G62">
-        <v>-9.603347520080067</v>
+        <v>-12.29091791031674</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.707057577987247</v>
       </c>
       <c r="E63">
-        <v>-7.642707659452864</v>
+        <v>-15.78156643990051</v>
       </c>
       <c r="F63">
-        <v>-3.146110047639648</v>
+        <v>-2.987931084511472</v>
       </c>
       <c r="G63">
-        <v>-10.00271187066451</v>
+        <v>-12.45990801791438</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.065601499140862</v>
       </c>
       <c r="E64">
-        <v>-7.252864917554546</v>
+        <v>-15.87836710028848</v>
       </c>
       <c r="F64">
-        <v>-2.96437345901931</v>
+        <v>-3.016803627055848</v>
       </c>
       <c r="G64">
-        <v>-10.02379673520413</v>
+        <v>-12.52199067841233</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.405861209446426</v>
       </c>
       <c r="E65">
-        <v>-8.155353559491187</v>
+        <v>-14.4654107543112</v>
       </c>
       <c r="F65">
-        <v>-3.320128445481092</v>
+        <v>-3.1377092796112</v>
       </c>
       <c r="G65">
-        <v>-9.177187613900767</v>
+        <v>-13.52455628952522</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.715312337870968</v>
       </c>
       <c r="E66">
-        <v>-7.130446679705194</v>
+        <v>-12.87397366226961</v>
       </c>
       <c r="F66">
-        <v>-3.430042387130336</v>
+        <v>-3.052775131366182</v>
       </c>
       <c r="G66">
-        <v>-9.393134499427426</v>
+        <v>-12.73278304453435</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.979060544700634</v>
       </c>
       <c r="E67">
-        <v>-7.674882467277362</v>
+        <v>-13.82296067531701</v>
       </c>
       <c r="F67">
-        <v>-3.42383901105956</v>
+        <v>-3.432562063241801</v>
       </c>
       <c r="G67">
-        <v>-9.81305733781074</v>
+        <v>-12.2080648871054</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.179775380603197</v>
       </c>
       <c r="E68">
-        <v>-7.846117654929401</v>
+        <v>-14.404484665012</v>
       </c>
       <c r="F68">
-        <v>-3.42446774230799</v>
+        <v>-3.041889528756409</v>
       </c>
       <c r="G68">
-        <v>-10.35621192334789</v>
+        <v>-12.3821433031969</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.308717988825382</v>
       </c>
       <c r="E69">
-        <v>-8.081992280566928</v>
+        <v>-14.01285317588066</v>
       </c>
       <c r="F69">
-        <v>-3.480582402156798</v>
+        <v>-2.984775550474958</v>
       </c>
       <c r="G69">
-        <v>-10.50200172780631</v>
+        <v>-12.96550777485403</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.351016213505248</v>
       </c>
       <c r="E70">
-        <v>-7.47041280888303</v>
+        <v>-14.47213553821259</v>
       </c>
       <c r="F70">
-        <v>-3.445787591341635</v>
+        <v>-3.035421673797754</v>
       </c>
       <c r="G70">
-        <v>-9.652750791162612</v>
+        <v>-12.15319921588306</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.302596232985443</v>
       </c>
       <c r="E71">
-        <v>-7.051877655672112</v>
+        <v>-13.61602752706251</v>
       </c>
       <c r="F71">
-        <v>-3.489691086729448</v>
+        <v>-3.503512088253488</v>
       </c>
       <c r="G71">
-        <v>-10.18920152198273</v>
+        <v>-12.03236430369966</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.164694295319151</v>
       </c>
       <c r="E72">
-        <v>-8.016419976935861</v>
+        <v>-14.6393403839978</v>
       </c>
       <c r="F72">
-        <v>-3.892928743947936</v>
+        <v>-3.483981035051331</v>
       </c>
       <c r="G72">
-        <v>-9.884131439993354</v>
+        <v>-12.61715893102976</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.940807232945649</v>
       </c>
       <c r="E73">
-        <v>-8.283418804428106</v>
+        <v>-15.29768087828491</v>
       </c>
       <c r="F73">
-        <v>-3.812708496360224</v>
+        <v>-3.963053658177679</v>
       </c>
       <c r="G73">
-        <v>-9.613755875255537</v>
+        <v>-11.02819638854577</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.645857052635741</v>
       </c>
       <c r="E74">
-        <v>-7.845048935063591</v>
+        <v>-15.97411262623265</v>
       </c>
       <c r="F74">
-        <v>-3.816593326970797</v>
+        <v>-3.907714222374478</v>
       </c>
       <c r="G74">
-        <v>-10.01532504916913</v>
+        <v>-11.34012261034698</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.291198027894737</v>
       </c>
       <c r="E75">
-        <v>-8.023049662883089</v>
+        <v>-15.62725415961514</v>
       </c>
       <c r="F75">
-        <v>-4.05281019093521</v>
+        <v>-3.957560574209977</v>
       </c>
       <c r="G75">
-        <v>-9.450992903817269</v>
+        <v>-12.77976630682768</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.894263855219297</v>
       </c>
       <c r="E76">
-        <v>-8.617008842203141</v>
+        <v>-15.23488000074653</v>
       </c>
       <c r="F76">
-        <v>-4.225445221659518</v>
+        <v>-3.966396861365172</v>
       </c>
       <c r="G76">
-        <v>-9.007747272109789</v>
+        <v>-12.06533402672526</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.475774184604075</v>
       </c>
       <c r="E77">
-        <v>-9.150983854817591</v>
+        <v>-15.67943576560552</v>
       </c>
       <c r="F77">
-        <v>-4.211343112335487</v>
+        <v>-4.139815034664664</v>
       </c>
       <c r="G77">
-        <v>-9.239561602406175</v>
+        <v>-10.70285252567389</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.050995017558726</v>
       </c>
       <c r="E78">
-        <v>-10.55400925729604</v>
+        <v>-16.44234778167775</v>
       </c>
       <c r="F78">
-        <v>-4.350837513073309</v>
+        <v>-4.088436447355978</v>
       </c>
       <c r="G78">
-        <v>-8.713654959128633</v>
+        <v>-11.79279005465922</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.642797120820637</v>
       </c>
       <c r="E79">
-        <v>-10.31297217128978</v>
+        <v>-16.01639045956826</v>
       </c>
       <c r="F79">
-        <v>-4.266064110978709</v>
+        <v>-3.749665123131368</v>
       </c>
       <c r="G79">
-        <v>-8.902481855597582</v>
+        <v>-11.0026058715272</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.265479049699696</v>
       </c>
       <c r="E80">
-        <v>-11.76570210447642</v>
+        <v>-17.44651425050861</v>
       </c>
       <c r="F80">
-        <v>-4.827354826705096</v>
+        <v>-4.358997557802611</v>
       </c>
       <c r="G80">
-        <v>-8.569301931434252</v>
+        <v>-10.86685033059831</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.92915976190516</v>
       </c>
       <c r="E81">
-        <v>-11.23646387567399</v>
+        <v>-16.42005410413799</v>
       </c>
       <c r="F81">
-        <v>-4.34862507590944</v>
+        <v>-4.222014122793718</v>
       </c>
       <c r="G81">
-        <v>-8.049662150862551</v>
+        <v>-12.273110485861</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.64696216010479</v>
       </c>
       <c r="E82">
-        <v>-12.23852460409129</v>
+        <v>-18.27152975912203</v>
       </c>
       <c r="F82">
-        <v>-4.768599337242292</v>
+        <v>-4.467909805460339</v>
       </c>
       <c r="G82">
-        <v>-8.187768179124326</v>
+        <v>-10.90964575278447</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.420356947564</v>
       </c>
       <c r="E83">
-        <v>-12.39076737175516</v>
+        <v>-17.77593809219659</v>
       </c>
       <c r="F83">
-        <v>-4.72629696853499</v>
+        <v>-4.651849329009054</v>
       </c>
       <c r="G83">
-        <v>-7.657054623723762</v>
+        <v>-11.36447498333386</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.259654639886938</v>
       </c>
       <c r="E84">
-        <v>-13.93598685807446</v>
+        <v>-18.33358796692314</v>
       </c>
       <c r="F84">
-        <v>-4.691274895920961</v>
+        <v>-4.783061739662085</v>
       </c>
       <c r="G84">
-        <v>-7.973628851462109</v>
+        <v>-11.99371368452867</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.173387148267712</v>
       </c>
       <c r="E85">
-        <v>-14.59445414963378</v>
+        <v>-21.54155895395683</v>
       </c>
       <c r="F85">
-        <v>-5.256223972312013</v>
+        <v>-4.279892239179368</v>
       </c>
       <c r="G85">
-        <v>-8.768328618709697</v>
+        <v>-11.5767703371307</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.165136567351631</v>
       </c>
       <c r="E86">
-        <v>-16.49814310992626</v>
+        <v>-22.33359811484639</v>
       </c>
       <c r="F86">
-        <v>-4.857125330503527</v>
+        <v>-3.976626017872995</v>
       </c>
       <c r="G86">
-        <v>-8.519839070532001</v>
+        <v>-11.17234747296225</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.249183987056157</v>
       </c>
       <c r="E87">
-        <v>-16.80554951098894</v>
+        <v>-22.31898472922363</v>
       </c>
       <c r="F87">
-        <v>-5.187995545916009</v>
+        <v>-4.139932228902407</v>
       </c>
       <c r="G87">
-        <v>-7.853949319671916</v>
+        <v>-11.15237495172383</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.429819421243367</v>
       </c>
       <c r="E88">
-        <v>-18.89268695333215</v>
+        <v>-23.33348064726599</v>
       </c>
       <c r="F88">
-        <v>-5.22748921218228</v>
+        <v>-5.339660726613983</v>
       </c>
       <c r="G88">
-        <v>-8.013623552122043</v>
+        <v>-10.11656153176004</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.712577611630959</v>
       </c>
       <c r="E89">
-        <v>-20.33066764667581</v>
+        <v>-24.48180202918303</v>
       </c>
       <c r="F89">
-        <v>-5.642015525166021</v>
+        <v>-4.721927523914291</v>
       </c>
       <c r="G89">
-        <v>-9.017069768348376</v>
+        <v>-10.68323423280817</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.106179475604017</v>
       </c>
       <c r="E90">
-        <v>-21.47275331988428</v>
+        <v>-26.40715068065419</v>
       </c>
       <c r="F90">
-        <v>-5.332496832905493</v>
+        <v>-5.108667716611647</v>
       </c>
       <c r="G90">
-        <v>-8.456687103824864</v>
+        <v>-10.48397249679944</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.604524872670798</v>
       </c>
       <c r="E91">
-        <v>-23.24030729455817</v>
+        <v>-27.91238826995977</v>
       </c>
       <c r="F91">
-        <v>-5.242973104917532</v>
+        <v>-4.314686258141573</v>
       </c>
       <c r="G91">
-        <v>-9.007091784093014</v>
+        <v>-10.9368683687539</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.210959635054014</v>
       </c>
       <c r="E92">
-        <v>-24.14008790903823</v>
+        <v>-29.96457494991178</v>
       </c>
       <c r="F92">
-        <v>-5.414331668673995</v>
+        <v>-5.010393221587925</v>
       </c>
       <c r="G92">
-        <v>-9.873537694267686</v>
+        <v>-11.98144811330567</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.922113527287033</v>
       </c>
       <c r="E93">
-        <v>-27.62230328197643</v>
+        <v>-31.49182092289464</v>
       </c>
       <c r="F93">
-        <v>-5.054055201823633</v>
+        <v>-4.747834577132008</v>
       </c>
       <c r="G93">
-        <v>-9.252154917637563</v>
+        <v>-12.26767125953998</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.724385980872997</v>
       </c>
       <c r="E94">
-        <v>-27.90639257037362</v>
+        <v>-32.10831605311387</v>
       </c>
       <c r="F94">
-        <v>-4.907752449355337</v>
+        <v>-5.209317770508528</v>
       </c>
       <c r="G94">
-        <v>-9.203281333841302</v>
+        <v>-10.48115191199998</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.614242279096349</v>
       </c>
       <c r="E95">
-        <v>-30.91799533901269</v>
+        <v>-31.92907225917926</v>
       </c>
       <c r="F95">
-        <v>-5.285859861107632</v>
+        <v>-3.940571369002101</v>
       </c>
       <c r="G95">
-        <v>-9.900439187319803</v>
+        <v>-12.14882929577122</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.574556077905799</v>
       </c>
       <c r="E96">
-        <v>-32.44546547145893</v>
+        <v>-36.86475797080436</v>
       </c>
       <c r="F96">
-        <v>-4.58782247440671</v>
+        <v>-4.197260007482442</v>
       </c>
       <c r="G96">
-        <v>-10.43242730275299</v>
+        <v>-10.71629996165441</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.576976692928641</v>
       </c>
       <c r="E97">
-        <v>-35.62182091720806</v>
+        <v>-38.8220957626657</v>
       </c>
       <c r="F97">
-        <v>-4.452069578894114</v>
+        <v>-4.40462808449121</v>
       </c>
       <c r="G97">
-        <v>-10.49473839089315</v>
+        <v>-11.58588757954585</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.6166339242435</v>
       </c>
       <c r="E98">
-        <v>-36.94607125008609</v>
+        <v>-41.11543047623717</v>
       </c>
       <c r="F98">
-        <v>-4.500407450845157</v>
+        <v>-4.305713772277651</v>
       </c>
       <c r="G98">
-        <v>-10.80857148692498</v>
+        <v>-13.06351978608969</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.63085738236498</v>
       </c>
       <c r="E99">
-        <v>-40.18265992861124</v>
+        <v>-41.41368935980437</v>
       </c>
       <c r="F99">
-        <v>-3.945329613425038</v>
+        <v>-4.142826451462873</v>
       </c>
       <c r="G99">
-        <v>-12.4613514157695</v>
+        <v>-12.23243050227444</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.64108835264354</v>
       </c>
       <c r="E100">
-        <v>-41.56006096091729</v>
+        <v>-45.08556401689481</v>
       </c>
       <c r="F100">
-        <v>-3.737980540887256</v>
+        <v>-4.237673015032626</v>
       </c>
       <c r="G100">
-        <v>-12.65218450283525</v>
+        <v>-12.57965045006982</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.54568481611205</v>
       </c>
       <c r="E101">
-        <v>-43.35448463611569</v>
+        <v>-46.20511600344111</v>
       </c>
       <c r="F101">
-        <v>-3.747958680007482</v>
+        <v>-4.237877313095717</v>
       </c>
       <c r="G101">
-        <v>-11.61134236419731</v>
+        <v>-13.29816463282216</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.43254214094754</v>
       </c>
       <c r="E102">
-        <v>-47.31054594379449</v>
+        <v>-48.53247314223221</v>
       </c>
       <c r="F102">
-        <v>-3.375091751129376</v>
+        <v>-3.660481891915226</v>
       </c>
       <c r="G102">
-        <v>-11.30478253671526</v>
+        <v>-14.65184173801184</v>
       </c>
     </row>
   </sheetData>
